--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -54,10 +54,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -208,6 +205,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -579,6 +585,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -592,34 +618,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -634,15 +640,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -654,35 +680,35 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -694,15 +720,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -714,17 +740,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -734,141 +760,126 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -904,7 +915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -922,24 +933,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -949,37 +955,37 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -989,22 +995,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1014,22 +1020,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1039,22 +1045,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1064,24 +1070,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -54,7 +54,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -209,10 +212,10 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
 4 error(s) during elaboration.
 </t>
   </si>
@@ -585,7 +588,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -605,7 +608,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -625,7 +628,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -640,7 +643,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +658,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -675,14 +678,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -695,14 +698,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -715,12 +718,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -735,7 +738,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -755,132 +758,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -933,6 +936,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -945,7 +953,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -955,22 +963,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +993,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -995,7 +1003,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1018,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1020,7 +1028,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +1043,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1045,7 +1053,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1060,7 +1068,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1070,7 +1078,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1093,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,10 +39,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -208,15 +205,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -588,6 +576,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -601,34 +609,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -643,15 +631,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -663,35 +671,35 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -703,15 +711,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -723,17 +731,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -743,147 +751,122 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -968,32 +951,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1003,22 +986,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1028,22 +1011,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1053,22 +1036,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1078,24 +1061,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -205,6 +205,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -741,7 +750,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -869,6 +878,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -205,15 +205,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -750,7 +741,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -878,11 +869,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,31 +39,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -901,7 +901,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -919,24 +919,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -946,12 +941,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -205,6 +205,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
 </t>
   </si>
 </sst>
@@ -741,7 +749,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -869,6 +877,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -209,10 +209,11 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
 </sst>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -205,15 +205,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -750,7 +741,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -878,11 +869,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -205,6 +211,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -576,7 +591,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -596,7 +611,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -616,7 +631,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -631,7 +646,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -646,7 +661,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -666,12 +681,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -686,12 +701,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -706,14 +721,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -726,7 +741,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -741,132 +756,137 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +946,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -959,37 +979,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1014,7 +1019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1039,7 +1044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1064,6 +1069,31 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
@@ -1071,7 +1101,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,10 +39,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -61,15 +61,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -211,15 +202,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
 </sst>
@@ -591,7 +573,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -611,7 +593,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -631,7 +613,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -646,6 +628,46 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -654,7 +676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -666,15 +688,15 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -686,17 +708,37 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -706,187 +748,122 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -966,42 +943,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1011,7 +978,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +993,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1036,7 +1003,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1051,7 +1018,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1061,7 +1028,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1043,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1086,7 +1053,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1068,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Post Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Post Verilog Run Checks.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -39,28 +39,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -573,7 +576,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -593,7 +596,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -613,7 +616,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -628,7 +631,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +646,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -663,14 +666,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -683,14 +686,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -703,12 +706,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +726,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -743,127 +746,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -943,17 +946,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +971,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -978,7 +981,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +996,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1003,7 +1006,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1021,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1028,7 +1031,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1046,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1053,7 +1056,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1071,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
